--- a/tg.xlsx
+++ b/tg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\User c driver data\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{008F96AC-16F2-4A38-9B82-3025C7AFC139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{987D82F2-48BC-4894-9061-DA1D2E8F295D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
   <si>
     <t>T</t>
   </si>
@@ -110,7 +110,10 @@
     <t>T6-2027</t>
   </si>
   <si>
-    <t>Mức an toàn</t>
+    <t>TG nhỏ</t>
+  </si>
+  <si>
+    <t>TG lớn</t>
   </si>
 </sst>
 </file>
@@ -172,8 +175,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -417,7 +420,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$I$1</c:f>
+              <c:f>Sheet1!$J$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -439,6 +442,21 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:dLbl>
+              <c:idx val="15"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-1251-4FB3-88BC-CB7587A1D994}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
             <c:spPr>
               <a:noFill/>
               <a:ln>
@@ -468,14 +486,334 @@
                 <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
             <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
+            <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$J$2:$J$17</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>43.75</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>87.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>131.25</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>218.75</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>262.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>306.25</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>393.75</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>437.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>481.25</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>525</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>568.75</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>612.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>656.25</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>700</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-51AF-4FD5-9473-6DBCBA651A37}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$K$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TG lớn</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="15"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-1251-4FB3-88BC-CB7587A1D994}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$K$2:$K$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>56.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>112.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>168.75</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>225</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>281.25</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>337.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>393.75</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>506.25</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>562.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>618.75</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>675</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>731.25</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>787.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>843.75</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>900</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-51AF-4FD5-9473-6DBCBA651A37}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$I$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TG nhỏ</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="15"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-1251-4FB3-88BC-CB7587A1D994}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -503,52 +841,52 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>43.75</c:v>
+                  <c:v>37.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>87.5</c:v>
+                  <c:v>75</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>131.25</c:v>
+                  <c:v>112.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>175</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>218.75</c:v>
+                  <c:v>187.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>225</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>262.5</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>306.25</c:v>
-                </c:pt>
                 <c:pt idx="7">
-                  <c:v>350</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>393.75</c:v>
+                  <c:v>337.5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>437.5</c:v>
+                  <c:v>375</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>481.25</c:v>
+                  <c:v>412.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>487.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>525</c:v>
                 </c:pt>
-                <c:pt idx="12">
-                  <c:v>568.75</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>612.5</c:v>
-                </c:pt>
                 <c:pt idx="14">
-                  <c:v>656.25</c:v>
+                  <c:v>562.5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>700</c:v>
+                  <c:v>600</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -556,97 +894,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-51AF-4FD5-9473-6DBCBA651A37}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$J$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Mức an toàn</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$J$2:$J$17</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
-                <c:pt idx="0">
-                  <c:v>560</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>560</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>560</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>560</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>560</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>560</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>560</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>560</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>560</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>560</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>560</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>560</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>560</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>560</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>560</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>560</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-51AF-4FD5-9473-6DBCBA651A37}"/>
+              <c16:uniqueId val="{00000000-1251-4FB3-88BC-CB7587A1D994}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -717,7 +965,7 @@
         <c:axId val="94239679"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="800"/>
+          <c:max val="1000"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -1386,16 +1634,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>187325</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>415925</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>73024</xdr:rowOff>
+      <xdr:rowOff>155574</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>492125</xdr:colOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>111125</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>76199</xdr:rowOff>
+      <xdr:rowOff>158749</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1687,14 +1935,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -1720,13 +1968,16 @@
         <v>5</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="4" t="s">
-        <v>24</v>
+      <c r="K1" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -1740,14 +1991,18 @@
         <f>SUM(B2:G2)</f>
         <v>0</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="4">
+        <v>37.5</v>
+      </c>
+      <c r="J2" s="4">
         <v>43.75</v>
       </c>
-      <c r="J2" s="1">
-        <v>560</v>
-      </c>
+      <c r="K2" s="1">
+        <v>56.25</v>
+      </c>
+      <c r="L2" s="5"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -1761,14 +2016,18 @@
         <f t="shared" ref="H3:H13" si="0">SUM(B3:G3)</f>
         <v>0</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3" s="4">
+        <v>75</v>
+      </c>
+      <c r="J3" s="4">
         <v>87.5</v>
       </c>
-      <c r="J3" s="1">
-        <v>560</v>
-      </c>
+      <c r="K3" s="1">
+        <v>112.5</v>
+      </c>
+      <c r="L3" s="5"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -1782,14 +2041,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="4">
+        <v>112.5</v>
+      </c>
+      <c r="J4" s="4">
         <v>131.25</v>
       </c>
-      <c r="J4" s="1">
-        <v>560</v>
-      </c>
+      <c r="K4" s="1">
+        <v>168.75</v>
+      </c>
+      <c r="L4" s="5"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -1803,14 +2066,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="4">
+        <v>150</v>
+      </c>
+      <c r="J5" s="4">
         <v>175</v>
       </c>
-      <c r="J5" s="1">
-        <v>560</v>
-      </c>
+      <c r="K5" s="1">
+        <v>225</v>
+      </c>
+      <c r="L5" s="5"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -1824,14 +2091,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6" s="4">
+        <v>187.5</v>
+      </c>
+      <c r="J6" s="4">
         <v>218.75</v>
       </c>
-      <c r="J6" s="1">
-        <v>560</v>
-      </c>
+      <c r="K6" s="1">
+        <v>281.25</v>
+      </c>
+      <c r="L6" s="5"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -1845,14 +2116,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="4">
+        <v>225</v>
+      </c>
+      <c r="J7" s="4">
         <v>262.5</v>
       </c>
-      <c r="J7" s="1">
-        <v>560</v>
-      </c>
+      <c r="K7" s="1">
+        <v>337.5</v>
+      </c>
+      <c r="L7" s="5"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -1866,14 +2141,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8" s="4">
+        <v>262.5</v>
+      </c>
+      <c r="J8" s="4">
         <v>306.25</v>
       </c>
-      <c r="J8" s="1">
-        <v>560</v>
-      </c>
+      <c r="K8" s="1">
+        <v>393.75</v>
+      </c>
+      <c r="L8" s="5"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -1887,14 +2166,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9" s="4">
+        <v>300</v>
+      </c>
+      <c r="J9" s="4">
         <v>350</v>
       </c>
-      <c r="J9" s="1">
-        <v>560</v>
-      </c>
+      <c r="K9" s="1">
+        <v>450</v>
+      </c>
+      <c r="L9" s="5"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -1908,14 +2191,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I10" s="4">
+        <v>337.5</v>
+      </c>
+      <c r="J10" s="4">
         <v>393.75</v>
       </c>
-      <c r="J10" s="1">
-        <v>560</v>
-      </c>
+      <c r="K10" s="1">
+        <v>506.25</v>
+      </c>
+      <c r="L10" s="5"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -1929,14 +2216,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11" s="4">
+        <v>375</v>
+      </c>
+      <c r="J11" s="4">
         <v>437.5</v>
       </c>
-      <c r="J11" s="1">
-        <v>560</v>
-      </c>
+      <c r="K11" s="1">
+        <v>562.5</v>
+      </c>
+      <c r="L11" s="5"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>18</v>
       </c>
@@ -1950,14 +2241,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I12" s="4">
+        <v>412.5</v>
+      </c>
+      <c r="J12" s="4">
         <v>481.25</v>
       </c>
-      <c r="J12" s="1">
-        <v>560</v>
-      </c>
+      <c r="K12" s="1">
+        <v>618.75</v>
+      </c>
+      <c r="L12" s="5"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>19</v>
       </c>
@@ -1971,14 +2266,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I13" s="5">
+      <c r="I13" s="4">
+        <v>450</v>
+      </c>
+      <c r="J13" s="4">
         <v>525</v>
       </c>
-      <c r="J13" s="1">
-        <v>560</v>
-      </c>
+      <c r="K13" s="1">
+        <v>675</v>
+      </c>
+      <c r="L13" s="5"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>21</v>
       </c>
@@ -1992,14 +2291,18 @@
         <f t="shared" ref="H14:H16" si="1">SUM(B14:G14)</f>
         <v>0</v>
       </c>
-      <c r="I14" s="5">
+      <c r="I14" s="4">
+        <v>487.5</v>
+      </c>
+      <c r="J14" s="4">
         <v>568.75</v>
       </c>
-      <c r="J14" s="1">
-        <v>560</v>
-      </c>
+      <c r="K14" s="1">
+        <v>731.25</v>
+      </c>
+      <c r="L14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>20</v>
       </c>
@@ -2013,14 +2316,18 @@
         <f t="shared" ref="H15:H17" si="2">SUM(B15:G15)</f>
         <v>0</v>
       </c>
-      <c r="I15" s="5">
+      <c r="I15" s="4">
+        <v>525</v>
+      </c>
+      <c r="J15" s="4">
         <v>612.5</v>
       </c>
-      <c r="J15" s="1">
-        <v>560</v>
-      </c>
+      <c r="K15" s="1">
+        <v>787.5</v>
+      </c>
+      <c r="L15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>22</v>
       </c>
@@ -2034,14 +2341,18 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I16" s="5">
+      <c r="I16" s="4">
+        <v>562.5</v>
+      </c>
+      <c r="J16" s="4">
         <v>656.25</v>
       </c>
-      <c r="J16" s="1">
-        <v>560</v>
-      </c>
+      <c r="K16" s="1">
+        <v>843.75</v>
+      </c>
+      <c r="L16" s="5"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>23</v>
       </c>
@@ -2055,12 +2366,16 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I17" s="5">
+      <c r="I17" s="4">
+        <v>600</v>
+      </c>
+      <c r="J17" s="4">
         <v>700</v>
       </c>
-      <c r="J17" s="1">
-        <v>560</v>
-      </c>
+      <c r="K17" s="1">
+        <v>900</v>
+      </c>
+      <c r="L17" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
